--- a/data/Oman 2020 Gas Data/OM20_gas_data.xlsx
+++ b/data/Oman 2020 Gas Data/OM20_gas_data.xlsx
@@ -8,24 +8,35 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tacaro/Documents/GitHub/Oman-2023/data/Oman 2020 Gas Data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82E29F2D-D182-B54B-9088-496569B9CD9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF2D8568-87A2-D549-8AF7-3409AF3B90DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" xr2:uid="{20AAA4A4-148D-4840-9148-6F668EF31271}"/>
+    <workbookView xWindow="30240" yWindow="500" windowWidth="38400" windowHeight="21100" xr2:uid="{20AAA4A4-148D-4840-9148-6F668EF31271}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="181029"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="32">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="33">
   <si>
     <t>Unique ID</t>
   </si>
@@ -121,13 +132,16 @@
   </si>
   <si>
     <t>NA</t>
+  </si>
+  <si>
+    <t>dilution_factor_H2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -135,13 +149,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="2">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -156,8 +184,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -472,7 +502,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5BBFDAFE-A619-2A48-83F8-EAB2FB289146}">
-  <dimension ref="A1:I14"/>
+  <dimension ref="A1:J14"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="4" width="33.33203125" customWidth="1"/>
@@ -480,9 +510,10 @@
     <col min="7" max="7" width="16.6640625" customWidth="1"/>
     <col min="8" max="8" width="18.33203125" customWidth="1"/>
     <col min="9" max="9" width="14" customWidth="1"/>
+    <col min="10" max="10" width="18.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -510,8 +541,11 @@
       <c r="I1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J1" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" t="s">
         <v>6</v>
       </c>
@@ -540,7 +574,7 @@
         <v>379.777554736539</v>
       </c>
     </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>7</v>
       </c>
@@ -569,7 +603,7 @@
         <v>3252.33442480331</v>
       </c>
     </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>8</v>
       </c>
@@ -598,36 +632,40 @@
         <v>14.9179780434264</v>
       </c>
     </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A5" t="s">
+    <row r="5" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="2">
         <v>55</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="E5">
+      <c r="E5" s="2">
         <v>36.200000000000003</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="2">
         <v>11.46</v>
       </c>
-      <c r="G5">
+      <c r="G5" s="2">
         <v>4.8197219884294702</v>
       </c>
-      <c r="H5">
+      <c r="H5" s="2">
         <v>1201.1806658243299</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="2">
         <v>16.141680546593399</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J5" s="2">
+        <f>G12/G5</f>
+        <v>34.577541140013132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -656,7 +694,7 @@
         <v>7.9535537096171902</v>
       </c>
     </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -685,7 +723,7 @@
         <v>417.55052099133798</v>
       </c>
     </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -714,7 +752,7 @@
         <v>405.14686166677802</v>
       </c>
     </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -743,7 +781,7 @@
         <v>56.772952286760301</v>
       </c>
     </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" t="s">
         <v>14</v>
       </c>
@@ -772,7 +810,7 @@
         <v>59.756842771576402</v>
       </c>
     </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" t="s">
         <v>15</v>
       </c>
@@ -801,36 +839,36 @@
         <v>4242.9673940554003</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A12" t="s">
+    <row r="12" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="2">
         <v>50</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="E12">
+      <c r="E12" s="2">
         <v>35.4</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="2">
         <v>10.87</v>
       </c>
-      <c r="G12">
+      <c r="G12" s="2">
         <v>166.6541353383459</v>
       </c>
-      <c r="H12">
+      <c r="H12" s="2">
         <v>1163.8909774436092</v>
       </c>
-      <c r="I12">
+      <c r="I12" s="2">
         <v>10.6</v>
       </c>
     </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
         <v>17</v>
       </c>
@@ -859,7 +897,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" t="s">
         <v>18</v>
       </c>
